--- a/atlas_max_plus_to_poly_mapping_template.xlsx
+++ b/atlas_max_plus_to_poly_mapping_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raeltonhonorio/Documents/KDAM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703945EE-EE2F-8E45-8AC6-7E631739921C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90D5927-5ED1-9F40-B7CC-89A7C4340FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="13" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="471">
   <si>
     <t>Atlas Max Plus → Atlas Max Poly Mapping Workbook</t>
   </si>
@@ -1975,7 +1975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2264,19 +2264,10 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2284,26 +2275,16 @@
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2317,6 +2298,12 @@
     <xf numFmtId="0" fontId="8" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="31" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2491,10 +2478,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="68.25" customHeight="1">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="210" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="185"/>
+      <c r="B1" s="211"/>
     </row>
     <row r="2" spans="1:2" ht="45.5" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -5142,171 +5129,171 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15">
-      <c r="A1" s="195" t="s">
+      <c r="A1" s="191" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="192" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="196" t="s">
+      <c r="A3" s="192" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="196" t="s">
+      <c r="A4" s="192" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="196" t="s">
+      <c r="A5" s="192" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="196" t="s">
+      <c r="A6" s="192" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="196" t="s">
+      <c r="A7" s="192" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="196" t="s">
+      <c r="A8" s="192" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="196" t="s">
+      <c r="A9" s="192" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="196" t="s">
+      <c r="A10" s="192" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="196" t="s">
+      <c r="A11" s="192" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="196" t="s">
+      <c r="A12" s="192" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="196" t="s">
+      <c r="A13" s="192" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="196" t="s">
+      <c r="A14" s="192" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="196" t="s">
+      <c r="A15" s="192" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="196" t="s">
+      <c r="A16" s="192" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="196" t="s">
+      <c r="A17" s="192" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="196" t="s">
+      <c r="A18" s="192" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="196" t="s">
+      <c r="A19" s="192" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="196" t="s">
+      <c r="A20" s="192" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="196" t="s">
+      <c r="A21" s="192" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="196" t="s">
+      <c r="A22" s="192" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="196" t="s">
+      <c r="A23" s="192" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="196" t="s">
+      <c r="A24" s="192" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="196" t="s">
+      <c r="A25" s="192" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="196" t="s">
+      <c r="A26" s="192" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="196" t="s">
+      <c r="A27" s="192" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="196" t="s">
+      <c r="A28" s="192" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="196" t="s">
+      <c r="A29" s="192" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="196" t="s">
+      <c r="A30" s="192" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="196" t="s">
+      <c r="A31" s="192" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="196"/>
+      <c r="A32" s="192"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="196"/>
+      <c r="A33" s="192"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="196"/>
+      <c r="A34" s="192"/>
     </row>
     <row r="35" spans="1:1" ht="15" thickBot="1">
-      <c r="A35" s="197"/>
+      <c r="A35" s="193"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A31" xr:uid="{8F8736C3-1C58-1646-B830-FED3997DCE44}"/>
@@ -5326,192 +5313,192 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="18">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="189" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="194" t="s">
+      <c r="A2" s="190" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="194" t="s">
+      <c r="A3" s="190" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="194" t="s">
+      <c r="A4" s="190" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="194" t="s">
+      <c r="A5" s="190" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="194" t="s">
+      <c r="A6" s="190" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="194" t="s">
+      <c r="A7" s="190" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="194" t="s">
+      <c r="A8" s="190" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="194" t="s">
+      <c r="A9" s="190" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="194" t="s">
+      <c r="A10" s="190" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="194" t="s">
+      <c r="A11" s="190" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="194" t="s">
+      <c r="A12" s="190" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="194" t="s">
+      <c r="A13" s="190" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="194" t="s">
+      <c r="A14" s="190" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="194" t="s">
+      <c r="A15" s="190" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="194" t="s">
+      <c r="A16" s="190" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="194" t="s">
+      <c r="A17" s="190" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="194" t="s">
+      <c r="A18" s="190" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="194" t="s">
+      <c r="A19" s="190" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="194" t="s">
+      <c r="A20" s="190" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="194" t="s">
+      <c r="A21" s="190" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="194" t="s">
+      <c r="A22" s="190" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="194" t="s">
+      <c r="A23" s="190" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="194" t="s">
+      <c r="A24" s="190" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="194" t="s">
+      <c r="A25" s="190" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="194" t="s">
+      <c r="A26" s="190" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="194" t="s">
+      <c r="A27" s="190" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="194" t="s">
+      <c r="A28" s="190" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="194" t="s">
+      <c r="A29" s="190" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="194" t="s">
+      <c r="A30" s="190" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="194" t="s">
+      <c r="A31" s="190" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="194" t="s">
+      <c r="A32" s="190" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="194" t="s">
+      <c r="A33" s="190" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="194" t="s">
+      <c r="A34" s="190" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="194"/>
+      <c r="A35" s="190"/>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="194"/>
+      <c r="A36" s="190"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="194"/>
+      <c r="A37" s="190"/>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="194"/>
+      <c r="A38" s="190"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="194"/>
+      <c r="A39" s="190"/>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="194"/>
+      <c r="A40" s="190"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A34" xr:uid="{4A1D7428-6F4D-D94B-B882-39478008AFA2}"/>
@@ -5539,8 +5526,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18">
-      <c r="A1" s="170" t="s">
-        <v>13</v>
+      <c r="A1" s="170">
+        <v>1</v>
       </c>
       <c r="B1" s="171" t="s">
         <v>14</v>
@@ -5552,52 +5539,52 @@
         <v>16</v>
       </c>
       <c r="E1" s="173"/>
-      <c r="F1" s="210" t="s">
+      <c r="F1" s="199" t="s">
         <v>390</v>
       </c>
-      <c r="G1" s="211" t="s">
+      <c r="G1" s="200" t="s">
         <v>462</v>
       </c>
-      <c r="H1" s="211" t="s">
+      <c r="H1" s="200" t="s">
         <v>463</v>
       </c>
-      <c r="I1" s="211" t="s">
+      <c r="I1" s="200" t="s">
         <v>464</v>
       </c>
-      <c r="J1" s="211" t="s">
+      <c r="J1" s="200" t="s">
         <v>466</v>
       </c>
-      <c r="K1" s="212" t="s">
+      <c r="K1" s="201" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="16">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="184" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="187" t="s">
+      <c r="B2" s="185" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="187" t="s">
+      <c r="C2" s="185" t="s">
         <v>230</v>
       </c>
-      <c r="D2" s="188" t="s">
-        <v>201</v>
+      <c r="D2" s="180" t="s">
+        <v>200</v>
       </c>
       <c r="E2" s="50"/>
       <c r="F2" s="74" t="s">
         <v>394</v>
       </c>
-      <c r="G2" s="198" t="s">
+      <c r="G2" s="75" t="s">
         <v>394</v>
       </c>
-      <c r="H2" s="198" t="s">
-        <v>200</v>
-      </c>
-      <c r="I2" s="198" t="s">
+      <c r="H2" s="75" t="s">
+        <v>200</v>
+      </c>
+      <c r="I2" s="75" t="s">
         <v>265</v>
       </c>
-      <c r="J2" s="198" t="s">
+      <c r="J2" s="75" t="s">
         <v>416</v>
       </c>
       <c r="K2" s="77" t="s">
@@ -5615,22 +5602,22 @@
         <v>317</v>
       </c>
       <c r="D3" s="180" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E3" s="50"/>
       <c r="F3" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="G3" s="199" t="s">
+      <c r="G3" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="H3" s="199" t="s">
-        <v>200</v>
-      </c>
-      <c r="I3" s="199" t="s">
+      <c r="H3" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="I3" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="J3" s="199" t="s">
+      <c r="J3" s="15" t="s">
         <v>421</v>
       </c>
       <c r="K3" s="12" t="s">
@@ -5647,23 +5634,23 @@
       <c r="C4" s="178" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="179" t="s">
-        <v>201</v>
+      <c r="D4" s="180" t="s">
+        <v>200</v>
       </c>
       <c r="E4" s="50"/>
       <c r="F4" s="74" t="s">
         <v>394</v>
       </c>
-      <c r="G4" s="198" t="s">
+      <c r="G4" s="75" t="s">
         <v>394</v>
       </c>
-      <c r="H4" s="198" t="s">
-        <v>200</v>
-      </c>
-      <c r="I4" s="198" t="s">
+      <c r="H4" s="75" t="s">
+        <v>200</v>
+      </c>
+      <c r="I4" s="75" t="s">
         <v>265</v>
       </c>
-      <c r="J4" s="198" t="s">
+      <c r="J4" s="75" t="s">
         <v>416</v>
       </c>
       <c r="K4" s="77" t="s">
@@ -5680,26 +5667,26 @@
       <c r="C5" s="178" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="179" t="s">
-        <v>201</v>
+      <c r="D5" s="180" t="s">
+        <v>200</v>
       </c>
       <c r="E5" s="50"/>
-      <c r="F5" s="74" t="s">
-        <v>394</v>
-      </c>
-      <c r="G5" s="198" t="s">
-        <v>394</v>
-      </c>
-      <c r="H5" s="198" t="s">
-        <v>200</v>
-      </c>
-      <c r="I5" s="198" t="s">
+      <c r="F5" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="J5" s="198" t="s">
-        <v>416</v>
-      </c>
-      <c r="K5" s="77" t="s">
+      <c r="J5" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="K5" s="12" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5713,26 +5700,26 @@
       <c r="C6" s="178" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="179" t="s">
-        <v>201</v>
+      <c r="D6" s="180" t="s">
+        <v>200</v>
       </c>
       <c r="E6" s="50"/>
       <c r="F6" s="168" t="s">
         <v>398</v>
       </c>
-      <c r="G6" s="200" t="s">
+      <c r="G6" s="194" t="s">
         <v>398</v>
       </c>
-      <c r="H6" s="200" t="s">
-        <v>200</v>
-      </c>
-      <c r="I6" s="200" t="s">
+      <c r="H6" s="194" t="s">
+        <v>200</v>
+      </c>
+      <c r="I6" s="194" t="s">
         <v>265</v>
       </c>
-      <c r="J6" s="200" t="s">
+      <c r="J6" s="194" t="s">
         <v>420</v>
       </c>
-      <c r="K6" s="213" t="s">
+      <c r="K6" s="202" t="s">
         <v>460</v>
       </c>
     </row>
@@ -5747,22 +5734,22 @@
         <v>318</v>
       </c>
       <c r="D7" s="180" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E7" s="50"/>
       <c r="F7" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="G7" s="199" t="s">
+      <c r="G7" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="H7" s="199" t="s">
-        <v>200</v>
-      </c>
-      <c r="I7" s="199" t="s">
+      <c r="H7" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="I7" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="J7" s="199" t="s">
+      <c r="J7" s="15" t="s">
         <v>421</v>
       </c>
       <c r="K7" s="12" t="s">
@@ -5779,26 +5766,26 @@
       <c r="C8" s="178" t="s">
         <v>204</v>
       </c>
-      <c r="D8" s="179" t="s">
-        <v>201</v>
+      <c r="D8" s="180" t="s">
+        <v>200</v>
       </c>
       <c r="E8" s="50"/>
       <c r="F8" s="168" t="s">
         <v>398</v>
       </c>
-      <c r="G8" s="200" t="s">
+      <c r="G8" s="194" t="s">
         <v>398</v>
       </c>
-      <c r="H8" s="200" t="s">
-        <v>200</v>
-      </c>
-      <c r="I8" s="200" t="s">
+      <c r="H8" s="194" t="s">
+        <v>200</v>
+      </c>
+      <c r="I8" s="194" t="s">
         <v>265</v>
       </c>
-      <c r="J8" s="200" t="s">
+      <c r="J8" s="194" t="s">
         <v>420</v>
       </c>
-      <c r="K8" s="213" t="s">
+      <c r="K8" s="202" t="s">
         <v>460</v>
       </c>
     </row>
@@ -5812,27 +5799,27 @@
       <c r="C9" s="178" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="179" t="s">
-        <v>201</v>
+      <c r="D9" s="180" t="s">
+        <v>200</v>
       </c>
       <c r="E9" s="50"/>
-      <c r="F9" s="168" t="s">
-        <v>398</v>
-      </c>
-      <c r="G9" s="200" t="s">
-        <v>398</v>
-      </c>
-      <c r="H9" s="200" t="s">
-        <v>200</v>
-      </c>
-      <c r="I9" s="200" t="s">
+      <c r="F9" t="s">
+        <v>395</v>
+      </c>
+      <c r="G9" t="s">
+        <v>395</v>
+      </c>
+      <c r="H9" t="s">
+        <v>200</v>
+      </c>
+      <c r="I9" t="s">
         <v>265</v>
       </c>
-      <c r="J9" s="200" t="s">
-        <v>420</v>
-      </c>
-      <c r="K9" s="213" t="s">
-        <v>460</v>
+      <c r="J9" t="s">
+        <v>421</v>
+      </c>
+      <c r="K9" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="16">
@@ -5846,22 +5833,22 @@
         <v>213</v>
       </c>
       <c r="D10" s="180" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E10" s="50"/>
       <c r="F10" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="G10" s="201" t="s">
+      <c r="G10" s="60" t="s">
         <v>401</v>
       </c>
-      <c r="H10" s="201" t="s">
-        <v>200</v>
-      </c>
-      <c r="I10" s="201" t="s">
+      <c r="H10" s="60" t="s">
+        <v>200</v>
+      </c>
+      <c r="I10" s="60" t="s">
         <v>265</v>
       </c>
-      <c r="J10" s="201" t="s">
+      <c r="J10" s="60" t="s">
         <v>424</v>
       </c>
       <c r="K10" s="52" t="s">
@@ -5878,26 +5865,26 @@
       <c r="C11" s="178" t="s">
         <v>319</v>
       </c>
-      <c r="D11" s="179" t="s">
-        <v>201</v>
+      <c r="D11" s="180" t="s">
+        <v>200</v>
       </c>
       <c r="E11" s="50"/>
-      <c r="F11" s="214" t="s">
+      <c r="F11" s="203" t="s">
         <v>399</v>
       </c>
-      <c r="G11" s="202" t="s">
+      <c r="G11" s="195" t="s">
         <v>399</v>
       </c>
-      <c r="H11" s="202" t="s">
-        <v>200</v>
-      </c>
-      <c r="I11" s="202" t="s">
+      <c r="H11" s="195" t="s">
+        <v>200</v>
+      </c>
+      <c r="I11" s="195" t="s">
         <v>265</v>
       </c>
-      <c r="J11" s="202" t="s">
+      <c r="J11" s="195" t="s">
         <v>422</v>
       </c>
-      <c r="K11" s="215" t="s">
+      <c r="K11" s="204" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5912,91 +5899,91 @@
         <v>207</v>
       </c>
       <c r="D12" s="180" t="s">
+        <v>200</v>
+      </c>
+      <c r="E12" s="50"/>
+      <c r="F12" s="205" t="s">
+        <v>400</v>
+      </c>
+      <c r="G12" s="196" t="s">
+        <v>400</v>
+      </c>
+      <c r="H12" s="196" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="50"/>
-      <c r="F12" s="216" t="s">
-        <v>400</v>
-      </c>
-      <c r="G12" s="203" t="s">
-        <v>400</v>
-      </c>
-      <c r="H12" s="203" t="s">
-        <v>201</v>
-      </c>
-      <c r="I12" s="203" t="s">
+      <c r="I12" s="196" t="s">
         <v>265</v>
       </c>
-      <c r="J12" s="203" t="s">
+      <c r="J12" s="196" t="s">
         <v>423</v>
       </c>
-      <c r="K12" s="217" t="s">
+      <c r="K12" s="206" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="16">
-      <c r="A13" s="189" t="s">
+      <c r="A13" s="186" t="s">
         <v>193</v>
       </c>
-      <c r="B13" s="190" t="s">
+      <c r="B13" s="187" t="s">
         <v>193</v>
       </c>
-      <c r="C13" s="190" t="s">
+      <c r="C13" s="187" t="s">
         <v>208</v>
       </c>
-      <c r="D13" s="179" t="s">
-        <v>201</v>
+      <c r="D13" s="180" t="s">
+        <v>200</v>
       </c>
       <c r="E13" s="50"/>
       <c r="F13" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="G13" s="201" t="s">
+      <c r="G13" s="60" t="s">
         <v>401</v>
       </c>
-      <c r="H13" s="201" t="s">
-        <v>200</v>
-      </c>
-      <c r="I13" s="201" t="s">
+      <c r="H13" s="60" t="s">
+        <v>200</v>
+      </c>
+      <c r="I13" s="60" t="s">
         <v>265</v>
       </c>
-      <c r="J13" s="201" t="s">
+      <c r="J13" s="60" t="s">
         <v>424</v>
       </c>
       <c r="K13" s="52" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15">
-      <c r="A14" s="186" t="s">
+    <row r="14" spans="1:11" ht="16">
+      <c r="A14" s="184" t="s">
         <v>194</v>
       </c>
-      <c r="B14" s="191" t="s">
+      <c r="B14" s="188" t="s">
         <v>194</v>
       </c>
-      <c r="C14" s="191" t="s">
+      <c r="C14" s="188" t="s">
         <v>209</v>
       </c>
-      <c r="D14" s="192" t="s">
+      <c r="D14" s="180" t="s">
+        <v>200</v>
+      </c>
+      <c r="E14" s="50"/>
+      <c r="F14" s="207" t="s">
+        <v>396</v>
+      </c>
+      <c r="G14" s="197" t="s">
+        <v>396</v>
+      </c>
+      <c r="H14" s="197" t="s">
         <v>201</v>
       </c>
-      <c r="E14" s="50"/>
-      <c r="F14" s="218" t="s">
-        <v>396</v>
-      </c>
-      <c r="G14" s="204" t="s">
-        <v>396</v>
-      </c>
-      <c r="H14" s="204" t="s">
-        <v>201</v>
-      </c>
-      <c r="I14" s="204" t="s">
+      <c r="I14" s="197" t="s">
         <v>265</v>
       </c>
-      <c r="J14" s="204" t="s">
+      <c r="J14" s="197" t="s">
         <v>419</v>
       </c>
-      <c r="K14" s="219" t="s">
+      <c r="K14" s="208" t="s">
         <v>327</v>
       </c>
     </row>
@@ -6010,23 +5997,23 @@
       <c r="C15" s="178" t="s">
         <v>320</v>
       </c>
-      <c r="D15" s="179" t="s">
-        <v>201</v>
+      <c r="D15" s="180" t="s">
+        <v>200</v>
       </c>
       <c r="E15" s="50"/>
       <c r="F15" s="169" t="s">
         <v>402</v>
       </c>
-      <c r="G15" s="205" t="s">
+      <c r="G15" s="45" t="s">
         <v>402</v>
       </c>
-      <c r="H15" s="205" t="s">
-        <v>200</v>
-      </c>
-      <c r="I15" s="205" t="s">
+      <c r="H15" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="I15" s="45" t="s">
         <v>265</v>
       </c>
-      <c r="J15" s="205" t="s">
+      <c r="J15" s="45" t="s">
         <v>428</v>
       </c>
       <c r="K15" s="132" t="s">
@@ -6043,23 +6030,23 @@
       <c r="C16" s="178" t="s">
         <v>210</v>
       </c>
-      <c r="D16" s="179" t="s">
-        <v>201</v>
+      <c r="D16" s="180" t="s">
+        <v>200</v>
       </c>
       <c r="E16" s="50"/>
-      <c r="F16" s="220" t="s">
+      <c r="F16" s="209" t="s">
         <v>403</v>
       </c>
-      <c r="G16" s="206" t="s">
+      <c r="G16" s="141" t="s">
         <v>459</v>
       </c>
-      <c r="H16" s="206" t="s">
-        <v>200</v>
-      </c>
-      <c r="I16" s="206" t="s">
+      <c r="H16" s="141" t="s">
+        <v>200</v>
+      </c>
+      <c r="I16" s="141" t="s">
         <v>265</v>
       </c>
-      <c r="J16" s="206" t="s">
+      <c r="J16" s="141" t="s">
         <v>428</v>
       </c>
       <c r="K16" s="142" t="s">
@@ -6076,26 +6063,26 @@
       <c r="C17" s="178" t="s">
         <v>204</v>
       </c>
-      <c r="D17" s="179" t="s">
-        <v>201</v>
+      <c r="D17" s="180" t="s">
+        <v>200</v>
       </c>
       <c r="E17" s="50"/>
       <c r="F17" s="168" t="s">
         <v>398</v>
       </c>
-      <c r="G17" s="200" t="s">
+      <c r="G17" s="194" t="s">
         <v>398</v>
       </c>
-      <c r="H17" s="200" t="s">
-        <v>200</v>
-      </c>
-      <c r="I17" s="200" t="s">
+      <c r="H17" s="194" t="s">
+        <v>200</v>
+      </c>
+      <c r="I17" s="194" t="s">
         <v>265</v>
       </c>
-      <c r="J17" s="200" t="s">
+      <c r="J17" s="194" t="s">
         <v>420</v>
       </c>
-      <c r="K17" s="213" t="s">
+      <c r="K17" s="202" t="s">
         <v>460</v>
       </c>
     </row>
@@ -6116,19 +6103,19 @@
       <c r="F18" s="168" t="s">
         <v>398</v>
       </c>
-      <c r="G18" s="200" t="s">
+      <c r="G18" s="194" t="s">
         <v>398</v>
       </c>
-      <c r="H18" s="200" t="s">
-        <v>200</v>
-      </c>
-      <c r="I18" s="200" t="s">
+      <c r="H18" s="194" t="s">
+        <v>200</v>
+      </c>
+      <c r="I18" s="194" t="s">
         <v>265</v>
       </c>
-      <c r="J18" s="200" t="s">
+      <c r="J18" s="194" t="s">
         <v>420</v>
       </c>
-      <c r="K18" s="213" t="s">
+      <c r="K18" s="202" t="s">
         <v>460</v>
       </c>
     </row>
@@ -6149,16 +6136,16 @@
       <c r="F19" s="74" t="s">
         <v>394</v>
       </c>
-      <c r="G19" s="198" t="s">
+      <c r="G19" s="75" t="s">
         <v>394</v>
       </c>
-      <c r="H19" s="198" t="s">
-        <v>200</v>
-      </c>
-      <c r="I19" s="198" t="s">
+      <c r="H19" s="75" t="s">
+        <v>200</v>
+      </c>
+      <c r="I19" s="75" t="s">
         <v>265</v>
       </c>
-      <c r="J19" s="198" t="s">
+      <c r="J19" s="75" t="s">
         <v>416</v>
       </c>
       <c r="K19" s="77" t="s">
@@ -6166,13 +6153,13 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="16">
-      <c r="A20" s="189" t="s">
+      <c r="A20" s="186" t="s">
         <v>193</v>
       </c>
-      <c r="B20" s="190" t="s">
+      <c r="B20" s="187" t="s">
         <v>193</v>
       </c>
-      <c r="C20" s="190" t="s">
+      <c r="C20" s="187" t="s">
         <v>248</v>
       </c>
       <c r="D20" s="179" t="s">
@@ -6182,16 +6169,16 @@
       <c r="F20" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="G20" s="201" t="s">
+      <c r="G20" s="60" t="s">
         <v>401</v>
       </c>
-      <c r="H20" s="201" t="s">
-        <v>200</v>
-      </c>
-      <c r="I20" s="201" t="s">
+      <c r="H20" s="60" t="s">
+        <v>200</v>
+      </c>
+      <c r="I20" s="60" t="s">
         <v>265</v>
       </c>
-      <c r="J20" s="201" t="s">
+      <c r="J20" s="60" t="s">
         <v>424</v>
       </c>
       <c r="K20" s="52" t="s">
@@ -6214,16 +6201,16 @@
       <c r="F21" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="G21" s="199" t="s">
+      <c r="G21" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="H21" s="199" t="s">
-        <v>200</v>
-      </c>
-      <c r="I21" s="199" t="s">
+      <c r="H21" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="I21" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="J21" s="199" t="s">
+      <c r="J21" s="15" t="s">
         <v>421</v>
       </c>
       <c r="K21" s="12" t="s">
@@ -6237,10 +6224,9 @@
       <c r="D22" s="176"/>
       <c r="E22" s="50"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="208"/>
-      <c r="H22" s="208"/>
-      <c r="I22" s="208"/>
-      <c r="J22" s="207"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
       <c r="K22" s="16"/>
     </row>
     <row r="23" spans="1:11" ht="16">
@@ -6250,10 +6236,9 @@
       <c r="D23" s="176"/>
       <c r="E23" s="50"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="208"/>
-      <c r="H23" s="208"/>
-      <c r="I23" s="208"/>
-      <c r="J23" s="207"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
       <c r="K23" s="16"/>
     </row>
     <row r="24" spans="1:11" ht="16">
@@ -6262,10 +6247,10 @@
       <c r="C24" s="175"/>
       <c r="D24" s="176"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="209"/>
-      <c r="H24" s="209"/>
-      <c r="I24" s="209"/>
-      <c r="J24" s="209"/>
+      <c r="G24" s="198"/>
+      <c r="H24" s="198"/>
+      <c r="I24" s="198"/>
+      <c r="J24" s="198"/>
       <c r="K24" s="16"/>
     </row>
     <row r="25" spans="1:11" ht="16">
@@ -6274,10 +6259,6 @@
       <c r="C25" s="175"/>
       <c r="D25" s="176"/>
       <c r="F25" s="7"/>
-      <c r="G25" s="207"/>
-      <c r="H25" s="207"/>
-      <c r="I25" s="207"/>
-      <c r="J25" s="207"/>
       <c r="K25" s="16"/>
     </row>
     <row r="26" spans="1:11" ht="16">
@@ -6286,10 +6267,6 @@
       <c r="C26" s="175"/>
       <c r="D26" s="176"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="207"/>
-      <c r="H26" s="207"/>
-      <c r="I26" s="207"/>
-      <c r="J26" s="207"/>
       <c r="K26" s="16"/>
     </row>
     <row r="27" spans="1:11" ht="16">
@@ -6298,10 +6275,6 @@
       <c r="C27" s="175"/>
       <c r="D27" s="176"/>
       <c r="F27" s="7"/>
-      <c r="G27" s="207"/>
-      <c r="H27" s="207"/>
-      <c r="I27" s="207"/>
-      <c r="J27" s="207"/>
       <c r="K27" s="16"/>
     </row>
     <row r="28" spans="1:11" ht="16">
@@ -6310,10 +6283,6 @@
       <c r="C28" s="175"/>
       <c r="D28" s="176"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="207"/>
-      <c r="H28" s="207"/>
-      <c r="I28" s="207"/>
-      <c r="J28" s="207"/>
       <c r="K28" s="16"/>
     </row>
     <row r="29" spans="1:11" ht="16">
@@ -6322,10 +6291,6 @@
       <c r="C29" s="175"/>
       <c r="D29" s="176"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="207"/>
-      <c r="H29" s="207"/>
-      <c r="I29" s="207"/>
-      <c r="J29" s="207"/>
       <c r="K29" s="16"/>
     </row>
     <row r="30" spans="1:11" ht="16">
@@ -6334,10 +6299,6 @@
       <c r="C30" s="175"/>
       <c r="D30" s="176"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="207"/>
-      <c r="H30" s="207"/>
-      <c r="I30" s="207"/>
-      <c r="J30" s="207"/>
       <c r="K30" s="16"/>
     </row>
     <row r="31" spans="1:11" ht="16">
@@ -6346,10 +6307,6 @@
       <c r="C31" s="175"/>
       <c r="D31" s="176"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="207"/>
-      <c r="H31" s="207"/>
-      <c r="I31" s="207"/>
-      <c r="J31" s="207"/>
       <c r="K31" s="16"/>
     </row>
     <row r="32" spans="1:11" ht="16">
@@ -6358,10 +6315,6 @@
       <c r="C32" s="175"/>
       <c r="D32" s="176"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="207"/>
-      <c r="H32" s="207"/>
-      <c r="I32" s="207"/>
-      <c r="J32" s="207"/>
       <c r="K32" s="16"/>
     </row>
     <row r="33" spans="1:11" ht="16">
@@ -6370,10 +6323,6 @@
       <c r="C33" s="175"/>
       <c r="D33" s="176"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="207"/>
-      <c r="H33" s="207"/>
-      <c r="I33" s="207"/>
-      <c r="J33" s="207"/>
       <c r="K33" s="16"/>
     </row>
     <row r="34" spans="1:11" ht="16">
@@ -6382,10 +6331,6 @@
       <c r="C34" s="175"/>
       <c r="D34" s="176"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="207"/>
-      <c r="H34" s="207"/>
-      <c r="I34" s="207"/>
-      <c r="J34" s="207"/>
       <c r="K34" s="16"/>
     </row>
     <row r="35" spans="1:11" ht="16">
@@ -6394,10 +6339,6 @@
       <c r="C35" s="175"/>
       <c r="D35" s="176"/>
       <c r="F35" s="7"/>
-      <c r="G35" s="207"/>
-      <c r="H35" s="207"/>
-      <c r="I35" s="207"/>
-      <c r="J35" s="207"/>
       <c r="K35" s="16"/>
     </row>
     <row r="36" spans="1:11" ht="16">
@@ -6406,10 +6347,6 @@
       <c r="C36" s="175"/>
       <c r="D36" s="176"/>
       <c r="F36" s="7"/>
-      <c r="G36" s="207"/>
-      <c r="H36" s="207"/>
-      <c r="I36" s="207"/>
-      <c r="J36" s="207"/>
       <c r="K36" s="16"/>
     </row>
     <row r="37" spans="1:11" ht="16">
@@ -6418,10 +6355,6 @@
       <c r="C37" s="175"/>
       <c r="D37" s="176"/>
       <c r="F37" s="7"/>
-      <c r="G37" s="207"/>
-      <c r="H37" s="207"/>
-      <c r="I37" s="207"/>
-      <c r="J37" s="207"/>
       <c r="K37" s="16"/>
     </row>
     <row r="38" spans="1:11" ht="16">
@@ -6430,10 +6363,6 @@
       <c r="C38" s="175"/>
       <c r="D38" s="176"/>
       <c r="F38" s="7"/>
-      <c r="G38" s="207"/>
-      <c r="H38" s="207"/>
-      <c r="I38" s="207"/>
-      <c r="J38" s="207"/>
       <c r="K38" s="16"/>
     </row>
     <row r="39" spans="1:11" ht="16">
@@ -6442,10 +6371,6 @@
       <c r="C39" s="175"/>
       <c r="D39" s="176"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="207"/>
-      <c r="H39" s="207"/>
-      <c r="I39" s="207"/>
-      <c r="J39" s="207"/>
       <c r="K39" s="16"/>
     </row>
     <row r="40" spans="1:11" ht="17" thickBot="1">
